--- a/accessories/cable-1/cable-1.xlsx
+++ b/accessories/cable-1/cable-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44916FB4-CA5F-4541-B951-38D2826C0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{44916FB4-CA5F-4541-B951-38D2826C0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495856D3-1205-4058-8ECB-54A4D72F9B4D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="42660" yWindow="2040" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Total Cost</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -71,13 +68,106 @@
     <t>MFR Part Number</t>
   </si>
   <si>
-    <t>Amount Per Cover</t>
-  </si>
-  <si>
     <t>Internal Part Name</t>
   </si>
   <si>
     <t>MFR / Vendor Description</t>
+  </si>
+  <si>
+    <t>8 AWG Blade Contact Crimp</t>
+  </si>
+  <si>
+    <t>Pin Contact Crimp</t>
+  </si>
+  <si>
+    <t>22 AWG Black Wire</t>
+  </si>
+  <si>
+    <t>22 AWG Red Wire</t>
+  </si>
+  <si>
+    <t>1339G5-BK</t>
+  </si>
+  <si>
+    <t>PM16P1620S30</t>
+  </si>
+  <si>
+    <t>1569-22-1-0500-001-1-TS</t>
+  </si>
+  <si>
+    <t>HOOK-UP STRAND 22AWG BLACK</t>
+  </si>
+  <si>
+    <t>CONTACT PIN 16-20AWG STD 7.7MM</t>
+  </si>
+  <si>
+    <t>TERM BLADE NON-GEND 8AWG SILVER</t>
+  </si>
+  <si>
+    <t>Amount Per Cable</t>
+  </si>
+  <si>
+    <t>5.5 ft</t>
+  </si>
+  <si>
+    <t>$69.62 (500 ft)</t>
+  </si>
+  <si>
+    <t>Total Cost (Per Cable)</t>
+  </si>
+  <si>
+    <t>22UL1007STRRED500</t>
+  </si>
+  <si>
+    <t>HOOK-UP STRND 22AWG RED 500'</t>
+  </si>
+  <si>
+    <t>$66.53 (500 ft)</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/remington-industries/22UL1007STRRED500/11613837</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/1569-22-1-0500-001-1-TS/7065706</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/pm16p1620s30/10650436</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/1339G5-BK/10650046</t>
+  </si>
+  <si>
+    <t>Needed</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/encore-wire/76843-38-03/2759985</t>
+  </si>
+  <si>
+    <t>8 AWG Red Wire</t>
+  </si>
+  <si>
+    <t>HOOK-UP STRND 8AWG 600V RED</t>
+  </si>
+  <si>
+    <t>76843.38.03</t>
+  </si>
+  <si>
+    <t>$436.97 (500 ft)</t>
+  </si>
+  <si>
+    <t>8 AWG Black Wire</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/prysmian-group/76843-38-01/2759983</t>
+  </si>
+  <si>
+    <t>HOOK-UP STRND 8AWG BLACK</t>
+  </si>
+  <si>
+    <t>76843.38.01</t>
+  </si>
+  <si>
+    <t>$461.54 (500 ft)</t>
   </si>
 </sst>
 </file>
@@ -571,131 +661,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.265625" customWidth="1"/>
+    <col min="2" max="2" width="33.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.06640625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.5703125" customWidth="1"/>
-    <col min="11" max="11" width="62.5703125" customWidth="1"/>
-    <col min="12" max="12" width="55.85546875" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.59765625" customWidth="1"/>
+    <col min="11" max="11" width="62.59765625" customWidth="1"/>
+    <col min="12" max="12" width="55.86328125" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="9">
+        <v>2.72</v>
+      </c>
+      <c r="F2" s="9">
+        <v>5.44</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="1"/>
+      <c r="E3" s="9">
+        <v>2.39</v>
+      </c>
+      <c r="F3" s="9">
+        <v>4.78</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="1"/>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.77</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="9">
+        <v>4.8</v>
+      </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="9">
+        <v>5.08</v>
+      </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -706,7 +889,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="10"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -716,7 +899,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="10"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -728,7 +911,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -739,7 +922,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -750,7 +933,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="10"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -761,7 +944,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="10"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -772,7 +955,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="10"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -783,7 +966,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="10"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -794,7 +977,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -805,7 +988,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -816,7 +999,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="10"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -827,7 +1010,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="10"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -838,7 +1021,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="10"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -849,7 +1032,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="10"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -860,7 +1043,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="12"/>
@@ -871,7 +1054,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -882,7 +1065,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -893,7 +1076,7 @@
       <c r="H25" s="1"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -903,7 +1086,7 @@
       <c r="G26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="11"/>
@@ -913,7 +1096,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -922,7 +1105,7 @@
       <c r="F28" s="9"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="13"/>
@@ -931,7 +1114,7 @@
       <c r="F29" s="9"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -940,7 +1123,7 @@
       <c r="F30" s="9"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="D31" s="2"/>
@@ -948,7 +1131,7 @@
       <c r="F31" s="9"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="D32" s="2"/>
@@ -956,7 +1139,7 @@
       <c r="F32" s="9"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -968,7 +1151,7 @@
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -980,7 +1163,7 @@
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -992,7 +1175,7 @@
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1004,7 +1187,7 @@
       <c r="I36" s="14"/>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -1016,7 +1199,7 @@
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1028,7 +1211,7 @@
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1040,7 +1223,7 @@
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1052,7 +1235,7 @@
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="18"/>
@@ -1062,22 +1245,25 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="E43" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" s="5">
         <f>SUM(F2:F42)</f>
-        <v>0</v>
+        <v>21.6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{95DCE46D-29B0-4CD2-BE72-78C260B1C72E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/accessories/cable-1/cable-1.xlsx
+++ b/accessories/cable-1/cable-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Battery-Lab-Hardware\accessories\cable-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{44916FB4-CA5F-4541-B951-38D2826C0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495856D3-1205-4058-8ECB-54A4D72F9B4D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42660" yWindow="2040" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -74,30 +74,12 @@
     <t>MFR / Vendor Description</t>
   </si>
   <si>
-    <t>8 AWG Blade Contact Crimp</t>
-  </si>
-  <si>
-    <t>Pin Contact Crimp</t>
-  </si>
-  <si>
-    <t>22 AWG Black Wire</t>
-  </si>
-  <si>
-    <t>22 AWG Red Wire</t>
-  </si>
-  <si>
     <t>1339G5-BK</t>
   </si>
   <si>
     <t>PM16P1620S30</t>
   </si>
   <si>
-    <t>1569-22-1-0500-001-1-TS</t>
-  </si>
-  <si>
-    <t>HOOK-UP STRAND 22AWG BLACK</t>
-  </si>
-  <si>
     <t>CONTACT PIN 16-20AWG STD 7.7MM</t>
   </si>
   <si>
@@ -107,67 +89,121 @@
     <t>Amount Per Cable</t>
   </si>
   <si>
-    <t>5.5 ft</t>
-  </si>
-  <si>
-    <t>$69.62 (500 ft)</t>
-  </si>
-  <si>
     <t>Total Cost (Per Cable)</t>
   </si>
   <si>
-    <t>22UL1007STRRED500</t>
-  </si>
-  <si>
-    <t>HOOK-UP STRND 22AWG RED 500'</t>
-  </si>
-  <si>
-    <t>$66.53 (500 ft)</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/remington-industries/22UL1007STRRED500/11613837</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/cnc-tech/1569-22-1-0500-001-1-TS/7065706</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/pm16p1620s30/10650436</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/1339G5-BK/10650046</t>
   </si>
   <si>
-    <t>Needed</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/encore-wire/76843-38-03/2759985</t>
-  </si>
-  <si>
-    <t>8 AWG Red Wire</t>
-  </si>
-  <si>
-    <t>HOOK-UP STRND 8AWG 600V RED</t>
-  </si>
-  <si>
-    <t>76843.38.03</t>
-  </si>
-  <si>
-    <t>$436.97 (500 ft)</t>
-  </si>
-  <si>
-    <t>8 AWG Black Wire</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/prysmian-group/76843-38-01/2759983</t>
-  </si>
-  <si>
-    <t>HOOK-UP STRND 8AWG BLACK</t>
-  </si>
-  <si>
-    <t>76843.38.01</t>
-  </si>
-  <si>
-    <t>$461.54 (500 ft)</t>
+    <t>8 AWG Red/black Wire</t>
+  </si>
+  <si>
+    <t>Wire-RB-08-50</t>
+  </si>
+  <si>
+    <t>Red/Black Bonded Zip Cord Easy ID Low Voltage Cable</t>
+  </si>
+  <si>
+    <t>https://powerwerx.com/red-black-bonded-zip-cord</t>
+  </si>
+  <si>
+    <t>Stranded Hookup Wire - Black</t>
+  </si>
+  <si>
+    <t>Stranded Hookup Wire - Red</t>
+  </si>
+  <si>
+    <t>Stranded Hookup Wire (300 Volt)</t>
+  </si>
+  <si>
+    <t>https://powerwerx.com/stranded-hookup-wire-300volt-ul1007</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/SBS75XBLK-BK/10650428</t>
+  </si>
+  <si>
+    <t>SBS75XBLK-BK</t>
+  </si>
+  <si>
+    <t>CONN HSG 6POS BLACK</t>
+  </si>
+  <si>
+    <t>SBS 75 connector</t>
+  </si>
+  <si>
+    <t>PM16S1620S32</t>
+  </si>
+  <si>
+    <t>CONTACT SOCKET 16-20AWG</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/PM16P1620S30/10650436</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/PM16S1620S32/10650063</t>
+  </si>
+  <si>
+    <t>Wire-ST-16-00-100</t>
+  </si>
+  <si>
+    <t>Wire-ST-16-02-100</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/remington-industries/16UL1007STRBLA/11613043</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/remington-industries/16UL1007STRRED/11613259</t>
+  </si>
+  <si>
+    <t>8 AWG main contact</t>
+  </si>
+  <si>
+    <t>SBS 75 auxiliary pin</t>
+  </si>
+  <si>
+    <t>SBS 75 auxiliary socket</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/techflex/NMN0-50BK100/2524519</t>
+  </si>
+  <si>
+    <t>SLEEVING 0.5" ID POLY 100' BLACK</t>
+  </si>
+  <si>
+    <t>Mesh Sleeving</t>
+  </si>
+  <si>
+    <t>NMN0.50BK100</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/qualtek/Q5-2X-3-4-01-QB48IN-5/754962</t>
+  </si>
+  <si>
+    <t>Adhesive Lined heat shrink</t>
+  </si>
+  <si>
+    <t>HEATSHRINK 0.752" X 4' BLK 1=1PC</t>
+  </si>
+  <si>
+    <t>Q5-2X-3/4-01-QB48IN-5</t>
+  </si>
+  <si>
+    <t>8 AWG Ring Terminal</t>
+  </si>
+  <si>
+    <t>CONN RING CIRC 8AWG #8 CRIMP</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0191930200/3044482</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0191930089/3187614</t>
+  </si>
+  <si>
+    <t>CONN RING CIRC 14-16AWG #8 CRIMP</t>
+  </si>
+  <si>
+    <t>16 AWG Ring Terminal</t>
   </si>
 </sst>
 </file>
@@ -180,7 +216,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,31 +248,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF150404"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -269,10 +286,10 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -300,28 +317,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -660,25 +675,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.265625" customWidth="1"/>
-    <col min="2" max="2" width="33.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.06640625" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.59765625" customWidth="1"/>
-    <col min="11" max="11" width="62.59765625" customWidth="1"/>
-    <col min="12" max="12" width="55.86328125" customWidth="1"/>
+    <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.5703125" customWidth="1"/>
+    <col min="11" max="11" width="62.5703125" customWidth="1"/>
+    <col min="12" max="12" width="55.85546875" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -689,13 +704,13 @@
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>8</v>
@@ -719,15 +734,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>2</v>
@@ -736,534 +751,357 @@
         <v>2.72</v>
       </c>
       <c r="F2" s="9">
+        <f>E2*D2</f>
         <v>5.44</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
+        <v>12.54</v>
+      </c>
+      <c r="F3" s="9">
+        <f t="shared" ref="F3:F6" si="0">E3*D3</f>
+        <v>12.54</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
+        <v>12.54</v>
+      </c>
+      <c r="F4" s="9">
+        <f t="shared" si="0"/>
+        <v>12.54</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="9">
-        <v>2.39</v>
-      </c>
-      <c r="F3" s="9">
-        <v>4.78</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.77</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
+        <v>128.19</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="0"/>
+        <v>128.19</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="B6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="9">
-        <v>0.73</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>38</v>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>6.15</v>
       </c>
       <c r="F6" s="9">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>6.15</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2.4</v>
       </c>
       <c r="F7" s="9">
-        <v>5.08</v>
+        <f t="shared" ref="F7:F12" si="1">D7*E7</f>
+        <v>4.8</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="10"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" si="1"/>
+        <v>4.8</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="10"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>72.62</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="1"/>
+        <v>72.62</v>
+      </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="10"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="H9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>6.22</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="1"/>
+        <v>6.22</v>
+      </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="1"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="10"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="H10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="17">
+        <v>191930200</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="10"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="H11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="16">
+        <v>191930089</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.42</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="10"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="9"/>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="10"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="9"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="10"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="10"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="10"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="10"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="10"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="10"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="10"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-    </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E43" s="7" t="s">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="5">
-        <f>SUM(F2:F42)</f>
-        <v>21.6</v>
+      <c r="F18" s="5">
+        <f>SUM(F2:F17)</f>
+        <v>255.14000000000004</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H5" r:id="rId1" xr:uid="{95DCE46D-29B0-4CD2-BE72-78C260B1C72E}"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{69C23E45-29AA-47FB-BE9B-2AE614B77C83}"/>
+    <hyperlink ref="H2" r:id="rId2" xr:uid="{F39CA3E8-0E7F-4D14-B47D-FB9B637BEFBF}"/>
+    <hyperlink ref="H3" r:id="rId3" xr:uid="{10C95AC9-075E-42F1-9F35-5641E1334E99}"/>
+    <hyperlink ref="H4" r:id="rId4" xr:uid="{75AF6812-83F6-4049-924E-6E150C43BB6C}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{B34F6116-3904-4136-83DC-1ED778E50D3C}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{CB356497-2003-425A-B8A7-BE51B9B913EE}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{21C1BAB4-A1A3-4E88-8334-DF28738598D1}"/>
+    <hyperlink ref="I3" r:id="rId8" xr:uid="{2F4C748B-C31C-4C18-98A1-F896819BEDE6}"/>
+    <hyperlink ref="I4" r:id="rId9" xr:uid="{6767DCFE-C4EA-4F98-917F-25EE5BC81B62}"/>
+    <hyperlink ref="H9" r:id="rId10" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
+    <hyperlink ref="H10" r:id="rId11" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
+    <hyperlink ref="H11" r:id="rId12" xr:uid="{8810426D-4117-48F2-9859-A19CAA6ADB2C}"/>
+    <hyperlink ref="H12" r:id="rId13" xr:uid="{CCA64CC5-DC08-4003-9DCA-627D9167BE5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
--- a/accessories/cable-1/cable-1.xlsx
+++ b/accessories/cable-1/cable-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Battery-Lab-Hardware\accessories\cable-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B08AE21-A859-440D-9224-0CB17283EA62}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="30615" yWindow="1815" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -204,19 +204,66 @@
   </si>
   <si>
     <t>16 AWG Ring Terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB50/120 T Handle </t>
+  </si>
+  <si>
+    <t>Connector T Handle For SBS® 50, SBS® 75X Series</t>
+  </si>
+  <si>
+    <t>113899P1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/113899P1/10647423?s=N4IgTCBcDaIIxwMwA4CcqAKcQF0C%2BQA</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 20 mm Lg, Low-Profile Std, Black Oxide, Alloy Steel, 50 PK</t>
+  </si>
+  <si>
+    <t>LHS4803020-050P1</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6EA45</t>
+  </si>
+  <si>
+    <t>T Handle Hex Nut</t>
+  </si>
+  <si>
+    <t>Hex Nut: Std Hex, M3x0.50 Thread, 5.5 mm Hex Wd, 2.4 mm Hex Ht, Steel, Class 8, Zinc-Plated, 100 PK</t>
+  </si>
+  <si>
+    <t>M01300.030.0001</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Short</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
+  </si>
+  <si>
+    <t>M07000.030.0018</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Long</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +303,12 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -327,16 +380,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -679,7 +732,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -741,7 +794,7 @@
       <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="2">
@@ -767,7 +820,7 @@
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="2">
@@ -795,7 +848,7 @@
       <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="2">
@@ -823,7 +876,7 @@
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="2">
@@ -846,10 +899,10 @@
       <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="2">
@@ -877,7 +930,7 @@
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="2">
@@ -887,7 +940,7 @@
         <v>2.4</v>
       </c>
       <c r="F7" s="9">
-        <f t="shared" ref="F7:F12" si="1">D7*E7</f>
+        <f t="shared" ref="F7:F13" si="1">D7*E7</f>
         <v>4.8</v>
       </c>
       <c r="G7" s="5"/>
@@ -903,7 +956,7 @@
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="2">
@@ -929,7 +982,7 @@
       <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="2">
@@ -955,7 +1008,7 @@
       <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="2">
@@ -981,7 +1034,7 @@
       <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="15">
         <v>191930200</v>
       </c>
       <c r="D11" s="2">
@@ -1007,7 +1060,7 @@
       <c r="B12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <v>191930089</v>
       </c>
       <c r="D12" s="2">
@@ -1027,49 +1080,105 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.72</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2.72</v>
+      </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="A14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.37</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.11</v>
+      </c>
       <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="H15" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="12">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="8"/>
@@ -1081,7 +1190,7 @@
       </c>
       <c r="F18" s="5">
         <f>SUM(F2:F17)</f>
-        <v>255.14000000000004</v>
+        <v>258.42000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1100,8 +1209,9 @@
     <hyperlink ref="H10" r:id="rId11" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
     <hyperlink ref="H11" r:id="rId12" xr:uid="{8810426D-4117-48F2-9859-A19CAA6ADB2C}"/>
     <hyperlink ref="H12" r:id="rId13" xr:uid="{CCA64CC5-DC08-4003-9DCA-627D9167BE5E}"/>
+    <hyperlink ref="H16" r:id="rId14" xr:uid="{DBEFA464-01ED-4E2E-BC80-A2D024432206}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId14"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/accessories/cable-1/cable-1.xlsx
+++ b/accessories/cable-1/cable-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B08AE21-A859-440D-9224-0CB17283EA62}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238A80B5-4592-4200-97EC-E835F6C3AEC0}"/>
   <bookViews>
-    <workbookView xWindow="30615" yWindow="1815" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -239,19 +239,7 @@
     <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
   </si>
   <si>
-    <t>SBS75 Handle Screws Short</t>
-  </si>
-  <si>
-    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
-  </si>
-  <si>
-    <t>M07000.030.0018</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
-  </si>
-  <si>
-    <t>SBS75 Handle Screws Long</t>
+    <t>SBS75 Handle Screws</t>
   </si>
 </sst>
 </file>
@@ -940,7 +928,7 @@
         <v>2.4</v>
       </c>
       <c r="F7" s="9">
-        <f t="shared" ref="F7:F13" si="1">D7*E7</f>
+        <f t="shared" ref="F7:F12" si="1">D7*E7</f>
         <v>4.8</v>
       </c>
       <c r="G7" s="5"/>
@@ -1106,7 +1094,7 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>60</v>
@@ -1115,13 +1103,13 @@
         <v>61</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8">
         <v>0.37</v>
       </c>
       <c r="F14" s="9">
-        <v>0.37</v>
+        <v>0.94</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="3" t="s">
@@ -1131,54 +1119,40 @@
       <c r="J14" s="11"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>67</v>
+      <c r="A15" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="13">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="F15" s="9">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="12">
-        <v>2</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0.04</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0.08</v>
-      </c>
+      <c r="A16" s="16"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="17" t="s">
-        <v>66</v>
-      </c>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="8"/>
@@ -1190,7 +1164,7 @@
       </c>
       <c r="F18" s="5">
         <f>SUM(F2:F17)</f>
-        <v>258.42000000000007</v>
+        <v>258.88000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1183,7 @@
     <hyperlink ref="H10" r:id="rId11" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
     <hyperlink ref="H11" r:id="rId12" xr:uid="{8810426D-4117-48F2-9859-A19CAA6ADB2C}"/>
     <hyperlink ref="H12" r:id="rId13" xr:uid="{CCA64CC5-DC08-4003-9DCA-627D9167BE5E}"/>
-    <hyperlink ref="H16" r:id="rId14" xr:uid="{DBEFA464-01ED-4E2E-BC80-A2D024432206}"/>
+    <hyperlink ref="H15" r:id="rId14" xr:uid="{2CA896D6-A65A-4B3D-8048-6D965D3E69AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId15"/>

--- a/accessories/cable-1/cable-1.xlsx
+++ b/accessories/cable-1/cable-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{00529C85-C1FB-4B8D-8F8E-701A9C9B067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238A80B5-4592-4200-97EC-E835F6C3AEC0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1964ACB6-83E9-4901-9217-17B693176A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="345" yWindow="3435" windowWidth="21600" windowHeight="11295" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -240,6 +240,18 @@
   </si>
   <si>
     <t>SBS75 Handle Screws</t>
+  </si>
+  <si>
+    <t>111038G2</t>
+  </si>
+  <si>
+    <t>SBS 75 small pin install tool</t>
+  </si>
+  <si>
+    <t>PP15/45 CONTACT INSERT/EXTRACTIO</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/111038G2/10650371</t>
   </si>
 </sst>
 </file>
@@ -1145,14 +1157,28 @@
       <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
+        <v>10.57</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0.08</v>
+      </c>
       <c r="G16" s="11"/>
-      <c r="H16" s="17"/>
+      <c r="H16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="8"/>
@@ -1164,7 +1190,7 @@
       </c>
       <c r="F18" s="5">
         <f>SUM(F2:F17)</f>
-        <v>258.88000000000005</v>
+        <v>258.96000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1184,8 +1210,9 @@
     <hyperlink ref="H11" r:id="rId12" xr:uid="{8810426D-4117-48F2-9859-A19CAA6ADB2C}"/>
     <hyperlink ref="H12" r:id="rId13" xr:uid="{CCA64CC5-DC08-4003-9DCA-627D9167BE5E}"/>
     <hyperlink ref="H15" r:id="rId14" xr:uid="{2CA896D6-A65A-4B3D-8048-6D965D3E69AC}"/>
+    <hyperlink ref="H16" r:id="rId15" xr:uid="{210F6856-A514-4749-9DFB-F485FEFC7C44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>